--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDA9B0F-76B0-4CC9-BE47-78449B0B42A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34359FB-D663-4B46-940F-54CE64EE8792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="114">
   <si>
     <t>S.No</t>
   </si>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t>Car Pooling App</t>
-  </si>
-  <si>
-    <t>Product Delivery App</t>
   </si>
   <si>
     <t>Versionrisers</t>
@@ -365,7 +362,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Movie recommendation system / Investor and Startup meeting </t>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor and Startup meeting </t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Food Delivery App</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -592,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -612,16 +624,29 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -633,15 +658,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -654,8 +676,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1559,19 +1585,19 @@
         <v>50</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1584,48 +1610,48 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>84</v>
+      <c r="D2" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="30"/>
+      <c r="I2" s="14"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
+      <c r="A3" s="28">
         <v>2</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="33">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="20"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="30"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="15"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="30"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1645,11 +1671,11 @@
         <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="30"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1666,14 +1692,16 @@
         <v>53</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>111</v>
+      </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="30"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1681,23 +1709,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="30"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1710,12 +1740,12 @@
       <c r="C8" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="28"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="17"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="30"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1728,12 +1758,12 @@
       <c r="C9" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="18"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="30"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1746,16 +1776,18 @@
       <c r="C10" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="30"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1763,17 +1795,17 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="2"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="30"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1786,12 +1818,12 @@
       <c r="C12" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="2"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="18"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="30"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1799,7 +1831,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2">
         <v>2301301020</v>
@@ -1808,14 +1840,14 @@
         <v>53</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="30"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1832,14 +1864,16 @@
         <v>53</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="30"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1856,14 +1890,14 @@
         <v>53</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="30"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1871,7 +1905,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2">
         <v>2301301023</v>
@@ -1880,14 +1914,16 @@
         <v>53</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" s="2"/>
+      <c r="G16" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="30"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1895,7 +1931,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2">
         <v>2301301029</v>
@@ -1904,14 +1940,16 @@
         <v>53</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="28"/>
+        <v>99</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="30"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1924,16 +1962,18 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="2"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>111</v>
+      </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="30"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1946,12 +1986,12 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="2"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="30"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1964,12 +2004,12 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="2"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="30"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1981,7 +2021,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="30"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1994,18 +2034,20 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="28"/>
+      <c r="F22" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="H22" s="2"/>
-      <c r="I22" s="30"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2013,17 +2055,17 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="28"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="30"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2031,17 +2073,17 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="28"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="30"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2054,18 +2096,18 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="25" t="s">
+      <c r="D25" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="31" t="s">
         <v>107</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>106</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="30"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2078,12 +2120,12 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="26"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="30"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2096,12 +2138,12 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="27"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="30"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2114,16 +2156,16 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>85</v>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>84</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="30"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2136,12 +2178,12 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="14"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="20"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="30"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2154,12 +2196,12 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="15"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="21"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="30"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2172,16 +2214,18 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G31" s="2"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="H31" s="2"/>
-      <c r="I31" s="30"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2189,17 +2233,17 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="2"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="30"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2216,14 +2260,16 @@
         <v>53</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="G33" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="30"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2240,14 +2286,14 @@
         <v>53</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="30"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2264,14 +2310,16 @@
         <v>53</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>111</v>
+      </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="30"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2284,14 +2332,16 @@
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16" t="s">
-        <v>76</v>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="G36" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="H36" s="2"/>
-      <c r="I36" s="30"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -2304,12 +2354,12 @@
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="30"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -2317,17 +2367,17 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="30"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -2344,14 +2394,14 @@
         <v>53</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="30"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -2364,14 +2414,16 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16" t="s">
-        <v>99</v>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25" t="s">
+        <v>98</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="G40" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="H40" s="2"/>
-      <c r="I40" s="30"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -2384,12 +2436,12 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="30"/>
+      <c r="I41" s="14"/>
       <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -2397,17 +2449,17 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="G42" s="18"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="30"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -2420,18 +2472,20 @@
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43" s="2"/>
+      <c r="F43" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="H43" s="2"/>
-      <c r="I43" s="30"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2439,17 +2493,17 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C44" s="3">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="2"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="18"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="30"/>
+      <c r="I44" s="14"/>
       <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -2463,11 +2517,13 @@
         <v>2301301080</v>
       </c>
       <c r="D45" s="2"/>
-      <c r="E45" s="16" t="s">
-        <v>59</v>
+      <c r="E45" s="25" t="s">
+        <v>58</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
+      <c r="G45" s="16" t="s">
+        <v>111</v>
+      </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -2477,15 +2533,15 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2">
         <v>2301301090</v>
       </c>
       <c r="D46" s="6"/>
-      <c r="E46" s="16"/>
+      <c r="E46" s="25"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="G46" s="17"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -2495,15 +2551,15 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" s="2">
         <v>2301301015</v>
       </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="16"/>
+      <c r="E47" s="25"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -2573,12 +2629,18 @@
       <c r="E63" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="44">
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="E2:E4"/>
@@ -2593,22 +2655,25 @@
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:E20"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F7:F9"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="E36:E38"/>
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="E31:E32"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="F25:F27"/>
     <mergeCell ref="F28:F30"/>
     <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G36:G38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2628,7 +2693,7 @@
         <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1">
         <v>2301301001</v>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34359FB-D663-4B46-940F-54CE64EE8792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B44E2F-0EA4-4E0B-9112-A37E1C327627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="112">
   <si>
     <t>S.No</t>
   </si>
@@ -300,9 +300,6 @@
     <t>Content Management System for Gyms and Library - Next and typescript and data modeling in MongoDB</t>
   </si>
   <si>
-    <t>Job Portal - "Career Karma" - MERN (90%) [Chatbot | Resume builder]</t>
-  </si>
-  <si>
     <t>20-21 Feb Linkedin API for Resume builder</t>
   </si>
   <si>
@@ -325,12 +322,6 @@
   </si>
   <si>
     <t>27-28 Feb</t>
-  </si>
-  <si>
-    <t>6-7 Mar</t>
-  </si>
-  <si>
-    <t>20-21 Mar</t>
   </si>
   <si>
     <t>27-28 Mar</t>
@@ -378,6 +369,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>Network Health Sentinen - App</t>
   </si>
 </sst>
 </file>
@@ -442,12 +436,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -461,6 +449,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -618,44 +612,57 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -664,25 +671,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1585,20 +1581,15 @@
         <v>50</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>103</v>
-      </c>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
@@ -1610,48 +1601,48 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="14"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="22">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="2"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="40"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="14"/>
+      <c r="I3" s="13"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="2"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="14"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1673,9 +1664,13 @@
       <c r="F5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="14"/>
+      <c r="G5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="13"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1692,16 +1687,16 @@
         <v>53</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>111</v>
+      <c r="G6" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="14"/>
+      <c r="I6" s="13"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1714,20 +1709,20 @@
       <c r="C7" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>108</v>
+      <c r="G7" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="14"/>
+      <c r="I7" s="13"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1740,12 +1735,12 @@
       <c r="C8" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="21"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="14"/>
+      <c r="I8" s="13"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,12 +1753,12 @@
       <c r="C9" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="14"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1776,18 +1771,18 @@
       <c r="C10" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>109</v>
+      <c r="G10" s="19" t="s">
+        <v>106</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="14"/>
+      <c r="I10" s="13"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1800,12 +1795,12 @@
       <c r="C11" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="21"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="14"/>
+      <c r="I11" s="13"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1818,12 +1813,12 @@
       <c r="C12" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="20"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="14"/>
+      <c r="I12" s="13"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1845,9 +1840,9 @@
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="39"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="14"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1869,11 +1864,11 @@
       <c r="F14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>113</v>
+      <c r="G14" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="14"/>
+      <c r="I14" s="13"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1895,9 +1890,9 @@
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="14"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1914,16 +1909,16 @@
         <v>53</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>108</v>
+      <c r="G16" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="14"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1942,14 +1937,16 @@
       <c r="E17" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="14"/>
+      <c r="F17" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="13"/>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1962,18 +1959,18 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="19" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>111</v>
+      <c r="G18" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="14"/>
+      <c r="I18" s="13"/>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1986,12 +1983,12 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="17"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="21"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="14"/>
+      <c r="I19" s="13"/>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2004,12 +2001,12 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="18"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="20"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="14"/>
+      <c r="I20" s="13"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2021,7 +2018,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="14"/>
+      <c r="I21" s="13"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2034,20 +2031,22 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="14"/>
+      <c r="G22" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="13"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2060,12 +2059,12 @@
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="14"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="13"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2078,12 +2077,12 @@
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="14"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="13"/>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2096,18 +2095,18 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25" s="2"/>
+      <c r="E25" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="39"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="14"/>
+      <c r="I25" s="13"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2120,12 +2119,12 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="2"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="39"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="14"/>
+      <c r="I26" s="13"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2138,12 +2137,12 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="2"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="39"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="14"/>
+      <c r="I27" s="13"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2156,16 +2155,16 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="2"/>
+      <c r="G28" s="39"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="14"/>
+      <c r="I28" s="13"/>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2178,12 +2177,12 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="2"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="39"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="14"/>
+      <c r="I29" s="13"/>
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2196,12 +2195,12 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="2"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="14"/>
+      <c r="I30" s="13"/>
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2214,18 +2213,18 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25" t="s">
+      <c r="D31" s="16"/>
+      <c r="E31" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="16" t="s">
-        <v>108</v>
+      <c r="G31" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="H31" s="2"/>
-      <c r="I31" s="14"/>
+      <c r="I31" s="13"/>
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2238,12 +2237,12 @@
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="18"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="20"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="14"/>
+      <c r="I32" s="13"/>
       <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2259,17 +2258,17 @@
       <c r="D33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>113</v>
+      <c r="G33" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="14"/>
+      <c r="I33" s="13"/>
       <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2286,14 +2285,18 @@
         <v>53</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="14"/>
+      <c r="G34" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" s="13"/>
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2315,11 +2318,11 @@
       <c r="F35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G35" s="39" t="s">
-        <v>111</v>
+      <c r="G35" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="14"/>
+      <c r="I35" s="13"/>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2332,16 +2335,16 @@
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25" t="s">
+      <c r="D36" s="16"/>
+      <c r="E36" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="16" t="s">
-        <v>108</v>
+      <c r="G36" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="H36" s="2"/>
-      <c r="I36" s="14"/>
+      <c r="I36" s="13"/>
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -2354,12 +2357,12 @@
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="17"/>
+      <c r="G37" s="21"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="14"/>
+      <c r="I37" s="13"/>
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -2372,12 +2375,12 @@
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="18"/>
+      <c r="G38" s="20"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="14"/>
+      <c r="I38" s="13"/>
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -2399,9 +2402,9 @@
       <c r="F39" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G39" s="2"/>
+      <c r="G39" s="39"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="14"/>
+      <c r="I39" s="13"/>
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -2414,16 +2417,16 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25" t="s">
-        <v>98</v>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16" t="s">
+        <v>97</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="16" t="s">
-        <v>109</v>
+      <c r="G40" s="19" t="s">
+        <v>106</v>
       </c>
       <c r="H40" s="2"/>
-      <c r="I40" s="14"/>
+      <c r="I40" s="13"/>
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -2436,12 +2439,12 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="17"/>
+      <c r="G41" s="21"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="14"/>
+      <c r="I41" s="13"/>
       <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -2454,12 +2457,12 @@
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="18"/>
+      <c r="G42" s="20"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="14"/>
+      <c r="I42" s="13"/>
       <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -2472,20 +2475,20 @@
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="E43" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="16" t="s">
-        <v>108</v>
+      <c r="G43" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="H43" s="2"/>
-      <c r="I43" s="14"/>
+      <c r="I43" s="13"/>
       <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2498,12 +2501,12 @@
       <c r="C44" s="3">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="18"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="20"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="14"/>
+      <c r="I44" s="13"/>
       <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -2517,12 +2520,12 @@
         <v>2301301080</v>
       </c>
       <c r="D45" s="2"/>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="16" t="s">
         <v>58</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="16" t="s">
-        <v>111</v>
+      <c r="G45" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2533,15 +2536,15 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46" s="2">
         <v>2301301090</v>
       </c>
       <c r="D46" s="6"/>
-      <c r="E46" s="25"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="17"/>
+      <c r="G46" s="21"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -2551,15 +2554,15 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2">
         <v>2301301015</v>
       </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="25"/>
+      <c r="E47" s="16"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="18"/>
+      <c r="G47" s="20"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -2629,20 +2632,34 @@
       <c r="E63" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
+  <mergeCells count="46">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="D43:D44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
@@ -2654,26 +2671,14 @@
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="D43:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B44E2F-0EA4-4E0B-9112-A37E1C327627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E98DB6-175E-4CDE-A9D6-8AD35AC13D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="112">
   <si>
     <t>S.No</t>
   </si>
@@ -359,9 +359,6 @@
     <t>D</t>
   </si>
   <si>
-    <t xml:space="preserve">Investor and Startup meeting </t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>Network Health Sentinen - App</t>
+  </si>
+  <si>
+    <t>Ecommerce</t>
   </si>
 </sst>
 </file>
@@ -598,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -625,21 +625,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -659,9 +663,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -671,14 +672,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1601,47 +1609,49 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="2"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="I2" s="13"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
+      <c r="A3" s="30">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="28">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="2"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="13"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="2"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="13"/>
       <c r="J4" s="2"/>
     </row>
@@ -1665,7 +1675,7 @@
         <v>83</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>105</v>
@@ -1687,13 +1697,13 @@
         <v>53</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="13"/>
@@ -1709,19 +1719,21 @@
       <c r="C7" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="24" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="I7" s="13"/>
       <c r="J7" s="2"/>
     </row>
@@ -1735,11 +1747,11 @@
       <c r="C8" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="2"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
       <c r="I8" s="13"/>
       <c r="J8" s="2"/>
     </row>
@@ -1753,11 +1765,11 @@
       <c r="C9" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="2"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="13"/>
       <c r="J9" s="2"/>
     </row>
@@ -1771,17 +1783,19 @@
       <c r="C10" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="27"/>
+      <c r="E10" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="22" t="s">
         <v>84</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="41" t="s">
+        <v>109</v>
+      </c>
       <c r="I10" s="13"/>
       <c r="J10" s="2"/>
     </row>
@@ -1795,11 +1809,11 @@
       <c r="C11" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="2"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="42"/>
       <c r="I11" s="13"/>
       <c r="J11" s="2"/>
     </row>
@@ -1813,11 +1827,11 @@
       <c r="C12" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="2"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="13"/>
       <c r="J12" s="2"/>
     </row>
@@ -1840,7 +1854,7 @@
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="39"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="2"/>
       <c r="I13" s="13"/>
       <c r="J13" s="2"/>
@@ -1865,7 +1879,7 @@
         <v>83</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="13"/>
@@ -1890,7 +1904,7 @@
       <c r="F15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="39"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="2"/>
       <c r="I15" s="13"/>
       <c r="J15" s="2"/>
@@ -1944,7 +1958,7 @@
         <v>105</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="2"/>
@@ -1959,17 +1973,19 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
+      <c r="D18" s="27"/>
+      <c r="E18" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="F18" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="I18" s="13"/>
       <c r="J18" s="2"/>
     </row>
@@ -1983,11 +1999,11 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="2"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="13"/>
       <c r="J19" s="2"/>
     </row>
@@ -2001,11 +2017,11 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="2"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="13"/>
       <c r="J20" s="2"/>
     </row>
@@ -2031,17 +2047,17 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="24" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H22" s="19" t="s">
         <v>105</v>
@@ -2059,11 +2075,11 @@
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="13"/>
       <c r="J23" s="2"/>
     </row>
@@ -2077,11 +2093,11 @@
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
       <c r="I24" s="13"/>
       <c r="J24" s="2"/>
     </row>
@@ -2095,17 +2111,19 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="2"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="I25" s="13"/>
       <c r="J25" s="2"/>
     </row>
@@ -2119,11 +2137,11 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="2"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="13"/>
       <c r="J26" s="2"/>
     </row>
@@ -2137,11 +2155,11 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="2"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="21"/>
       <c r="I27" s="13"/>
       <c r="J27" s="2"/>
     </row>
@@ -2155,15 +2173,17 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="2"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="I28" s="13"/>
       <c r="J28" s="2"/>
     </row>
@@ -2177,11 +2197,11 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="2"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="13"/>
       <c r="J29" s="2"/>
     </row>
@@ -2195,11 +2215,11 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="2"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="13"/>
       <c r="J30" s="2"/>
     </row>
@@ -2213,11 +2233,11 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16" t="s">
+      <c r="D31" s="27"/>
+      <c r="E31" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="22" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="19" t="s">
@@ -2237,10 +2257,10 @@
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="21"/>
       <c r="H32" s="2"/>
       <c r="I32" s="13"/>
       <c r="J32" s="2"/>
@@ -2265,7 +2285,7 @@
         <v>90</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="13"/>
@@ -2285,16 +2305,16 @@
         <v>53</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>92</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="2"/>
@@ -2319,7 +2339,7 @@
         <v>83</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="13"/>
@@ -2335,8 +2355,8 @@
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16" t="s">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F36" s="2"/>
@@ -2357,10 +2377,10 @@
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="21"/>
+      <c r="G37" s="20"/>
       <c r="H37" s="2"/>
       <c r="I37" s="13"/>
       <c r="J37" s="2"/>
@@ -2375,10 +2395,10 @@
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="20"/>
+      <c r="G38" s="21"/>
       <c r="H38" s="2"/>
       <c r="I38" s="13"/>
       <c r="J38" s="2"/>
@@ -2402,7 +2422,7 @@
       <c r="F39" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G39" s="39"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="2"/>
       <c r="I39" s="13"/>
       <c r="J39" s="2"/>
@@ -2417,8 +2437,8 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16" t="s">
+      <c r="D40" s="27"/>
+      <c r="E40" s="27" t="s">
         <v>97</v>
       </c>
       <c r="F40" s="2"/>
@@ -2439,10 +2459,10 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="21"/>
+      <c r="G41" s="20"/>
       <c r="H41" s="2"/>
       <c r="I41" s="13"/>
       <c r="J41" s="2"/>
@@ -2457,10 +2477,10 @@
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="20"/>
+      <c r="G42" s="21"/>
       <c r="H42" s="2"/>
       <c r="I42" s="13"/>
       <c r="J42" s="2"/>
@@ -2475,13 +2495,13 @@
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="39" t="s">
         <v>82</v>
       </c>
       <c r="G43" s="19" t="s">
@@ -2501,10 +2521,10 @@
       <c r="C44" s="3">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="21"/>
       <c r="H44" s="2"/>
       <c r="I44" s="13"/>
       <c r="J44" s="2"/>
@@ -2520,12 +2540,12 @@
         <v>2301301080</v>
       </c>
       <c r="D45" s="2"/>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="27" t="s">
         <v>58</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2542,9 +2562,9 @@
         <v>2301301090</v>
       </c>
       <c r="D46" s="6"/>
-      <c r="E46" s="16"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="21"/>
+      <c r="G46" s="20"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -2560,9 +2580,9 @@
         <v>2301301015</v>
       </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="16"/>
+      <c r="E47" s="27"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="20"/>
+      <c r="G47" s="21"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -2632,29 +2652,20 @@
       <c r="E63" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
+  <mergeCells count="52">
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="D43:D44"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2671,14 +2682,29 @@
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="H18:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E98DB6-175E-4CDE-A9D6-8AD35AC13D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78908C-CE28-454F-B5CD-E6F3E7DF2C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
   <si>
     <t>S.No</t>
   </si>
@@ -626,8 +626,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -639,9 +637,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1615,11 +1615,11 @@
       <c r="E2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>83</v>
       </c>
       <c r="G2" s="16"/>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="17" t="s">
         <v>109</v>
       </c>
       <c r="I2" s="13"/>
@@ -1637,9 +1637,9 @@
       </c>
       <c r="D3" s="34"/>
       <c r="E3" s="34"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="13"/>
       <c r="J3" s="2"/>
     </row>
@@ -1649,9 +1649,9 @@
       <c r="C4" s="29"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="21"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="19"/>
       <c r="I4" s="13"/>
       <c r="J4" s="2"/>
     </row>
@@ -1725,13 +1725,13 @@
       <c r="E7" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>109</v>
       </c>
       <c r="I7" s="13"/>
@@ -1749,9 +1749,9 @@
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="36"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="I8" s="13"/>
       <c r="J8" s="2"/>
     </row>
@@ -1767,9 +1767,9 @@
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="36"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="13"/>
       <c r="J9" s="2"/>
     </row>
@@ -1787,10 +1787,10 @@
       <c r="E10" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="17" t="s">
         <v>106</v>
       </c>
       <c r="H10" s="41" t="s">
@@ -1811,8 +1811,8 @@
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="27"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="18"/>
       <c r="H11" s="42"/>
       <c r="I11" s="13"/>
       <c r="J11" s="2"/>
@@ -1829,8 +1829,8 @@
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="43"/>
       <c r="I12" s="13"/>
       <c r="J12" s="2"/>
@@ -1977,13 +1977,13 @@
       <c r="E18" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="17" t="s">
         <v>109</v>
       </c>
       <c r="I18" s="13"/>
@@ -2001,9 +2001,9 @@
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="13"/>
       <c r="J19" s="2"/>
     </row>
@@ -2019,9 +2019,9 @@
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="13"/>
       <c r="J20" s="2"/>
     </row>
@@ -2053,13 +2053,13 @@
       <c r="E22" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="17" t="s">
         <v>105</v>
       </c>
       <c r="I22" s="13"/>
@@ -2077,9 +2077,9 @@
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="27"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="13"/>
       <c r="J23" s="2"/>
     </row>
@@ -2095,9 +2095,9 @@
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="27"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="13"/>
       <c r="J24" s="2"/>
     </row>
@@ -2117,11 +2117,11 @@
       <c r="E25" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="23" t="s">
         <v>103</v>
       </c>
       <c r="G25" s="16"/>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="17" t="s">
         <v>109</v>
       </c>
       <c r="I25" s="13"/>
@@ -2139,9 +2139,9 @@
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="27"/>
-      <c r="F26" s="25"/>
+      <c r="F26" s="24"/>
       <c r="G26" s="16"/>
-      <c r="H26" s="20"/>
+      <c r="H26" s="18"/>
       <c r="I26" s="13"/>
       <c r="J26" s="2"/>
     </row>
@@ -2157,9 +2157,9 @@
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="27"/>
-      <c r="F27" s="26"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="16"/>
-      <c r="H27" s="21"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="13"/>
       <c r="J27" s="2"/>
     </row>
@@ -2177,11 +2177,11 @@
       <c r="E28" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="20" t="s">
         <v>84</v>
       </c>
       <c r="G28" s="16"/>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="17" t="s">
         <v>109</v>
       </c>
       <c r="I28" s="13"/>
@@ -2199,9 +2199,9 @@
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="23"/>
+      <c r="F29" s="21"/>
       <c r="G29" s="16"/>
-      <c r="H29" s="20"/>
+      <c r="H29" s="18"/>
       <c r="I29" s="13"/>
       <c r="J29" s="2"/>
     </row>
@@ -2217,9 +2217,9 @@
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="18"/>
+      <c r="F30" s="22"/>
       <c r="G30" s="16"/>
-      <c r="H30" s="21"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="13"/>
       <c r="J30" s="2"/>
     </row>
@@ -2237,10 +2237,10 @@
       <c r="E31" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="17" t="s">
         <v>105</v>
       </c>
       <c r="H31" s="2"/>
@@ -2259,8 +2259,8 @@
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="2"/>
       <c r="I32" s="13"/>
       <c r="J32" s="2"/>
@@ -2360,7 +2360,7 @@
         <v>75</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="17" t="s">
         <v>105</v>
       </c>
       <c r="H36" s="2"/>
@@ -2380,7 +2380,7 @@
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="20"/>
+      <c r="G37" s="18"/>
       <c r="H37" s="2"/>
       <c r="I37" s="13"/>
       <c r="J37" s="2"/>
@@ -2398,7 +2398,7 @@
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="21"/>
+      <c r="G38" s="19"/>
       <c r="H38" s="2"/>
       <c r="I38" s="13"/>
       <c r="J38" s="2"/>
@@ -2442,10 +2442,12 @@
         <v>97</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H40" s="2"/>
+      <c r="H40" s="17" t="s">
+        <v>105</v>
+      </c>
       <c r="I40" s="13"/>
       <c r="J40" s="2"/>
     </row>
@@ -2462,8 +2464,8 @@
       <c r="D41" s="27"/>
       <c r="E41" s="27"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="2"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
       <c r="I41" s="13"/>
       <c r="J41" s="2"/>
     </row>
@@ -2480,8 +2482,8 @@
       <c r="D42" s="27"/>
       <c r="E42" s="27"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="2"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
       <c r="I42" s="13"/>
       <c r="J42" s="2"/>
     </row>
@@ -2504,7 +2506,7 @@
       <c r="F43" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="17" t="s">
         <v>105</v>
       </c>
       <c r="H43" s="2"/>
@@ -2521,10 +2523,10 @@
       <c r="C44" s="3">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="18"/>
+      <c r="D44" s="22"/>
       <c r="E44" s="38"/>
       <c r="F44" s="40"/>
-      <c r="G44" s="21"/>
+      <c r="G44" s="19"/>
       <c r="H44" s="2"/>
       <c r="I44" s="13"/>
       <c r="J44" s="2"/>
@@ -2544,7 +2546,7 @@
         <v>58</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="19" t="s">
+      <c r="G45" s="17" t="s">
         <v>107</v>
       </c>
       <c r="H45" s="2"/>
@@ -2564,7 +2566,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="27"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="20"/>
+      <c r="G46" s="18"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -2582,7 +2584,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="27"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="21"/>
+      <c r="G47" s="19"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -2652,12 +2654,15 @@
       <c r="E63" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="53">
+    <mergeCell ref="H40:H42"/>
     <mergeCell ref="H28:H30"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H7:H9"/>
     <mergeCell ref="H25:H27"/>
     <mergeCell ref="H10:H12"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="G43:G44"/>
@@ -2666,6 +2671,7 @@
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="D43:D44"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2688,7 +2694,6 @@
     <mergeCell ref="E36:E38"/>
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="E31:E32"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="G22:G24"/>
     <mergeCell ref="G31:G32"/>
     <mergeCell ref="G36:G38"/>
@@ -2700,11 +2705,9 @@
     <mergeCell ref="F22:F24"/>
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H22:H24"/>
     <mergeCell ref="G7:G9"/>
     <mergeCell ref="G10:G12"/>
     <mergeCell ref="G18:G20"/>
-    <mergeCell ref="H18:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78908C-CE28-454F-B5CD-E6F3E7DF2C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67B9875-E30E-40AA-BC3A-CBF87DA6145B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BTech 6th Sem Attendance" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
   <si>
     <t>S.No</t>
   </si>
@@ -234,9 +234,6 @@
     <t>Aryan</t>
   </si>
   <si>
-    <t>Humanshu</t>
-  </si>
-  <si>
     <t>Kartikay</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
   </si>
   <si>
     <t>Vaibhav Pratap</t>
-  </si>
-  <si>
-    <t>solo</t>
   </si>
   <si>
     <t>"NotesCraftr" - MERN</t>
@@ -373,12 +367,36 @@
   <si>
     <t>Ecommerce</t>
   </si>
+  <si>
+    <t>#Check 1</t>
+  </si>
+  <si>
+    <t>#Check 2</t>
+  </si>
+  <si>
+    <t>#Check 3</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>Sr. No.</t>
+  </si>
+  <si>
+    <t>Github URL</t>
+  </si>
+  <si>
+    <t>Functionality</t>
+  </si>
+  <si>
+    <t>Viva</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,8 +420,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,8 +497,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -517,24 +562,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -598,11 +625,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -618,7 +644,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -635,32 +661,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -672,21 +701,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1558,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B259E3A8-2371-44C6-BEBA-5395376E3076}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" customWidth="1"/>
@@ -1572,34 +1601,42 @@
     <col min="10" max="10" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" s="12" t="s">
+      <c r="F1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1609,53 +1646,56 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" s="13"/>
+      <c r="D2" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="12"/>
       <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="30">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="25">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="13"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="13"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1665,25 +1705,26 @@
       <c r="C5" s="2">
         <v>2301301014</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="13"/>
+      <c r="H5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="12"/>
       <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1693,23 +1734,24 @@
       <c r="C6" s="2">
         <v>2301301008</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>108</v>
+      <c r="E6" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>107</v>
+        <v>81</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="13"/>
+      <c r="I6" s="12"/>
       <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1719,25 +1761,26 @@
       <c r="C7" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I7" s="13"/>
+      <c r="E7" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="12"/>
       <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1747,15 +1790,16 @@
       <c r="C8" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="13"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="12"/>
       <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1765,15 +1809,16 @@
       <c r="C9" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="13"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1783,23 +1828,24 @@
       <c r="C10" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27" t="s">
+      <c r="D10" s="22"/>
+      <c r="E10" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="13"/>
+      <c r="F10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="12"/>
       <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1809,15 +1855,16 @@
       <c r="C11" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="13"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1827,15 +1874,16 @@
       <c r="C12" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="13"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1845,21 +1893,22 @@
       <c r="C13" s="2">
         <v>2301301020</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="16"/>
+        <v>82</v>
+      </c>
+      <c r="G13" s="15"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="13"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1869,23 +1918,24 @@
       <c r="C14" s="2">
         <v>2301301027</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>109</v>
+        <v>81</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="13"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1895,21 +1945,22 @@
       <c r="C15" s="2">
         <v>2301301097</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="16"/>
+        <v>81</v>
+      </c>
+      <c r="G15" s="15"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="13"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1919,23 +1970,24 @@
       <c r="C16" s="2">
         <v>2301301023</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>93</v>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>105</v>
+        <v>92</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="13"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1945,25 +1997,26 @@
       <c r="C17" s="2">
         <v>2301301029</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="13"/>
+      <c r="E17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="12"/>
       <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1973,23 +2026,24 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="17" t="s">
+      <c r="D18" s="22"/>
+      <c r="E18" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="13"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1999,15 +2053,16 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="13"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2017,27 +2072,29 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="13"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="13"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -2047,43 +2104,45 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="13"/>
+      <c r="F22" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="12"/>
       <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="13"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -2093,15 +2152,16 @@
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="13"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -2111,23 +2171,24 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="13"/>
+      <c r="D25" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="12"/>
       <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -2137,15 +2198,16 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="13"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -2155,15 +2217,16 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="13"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -2173,21 +2236,22 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27" t="s">
+      <c r="D28" s="22"/>
+      <c r="E28" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I28" s="13"/>
+      <c r="F28" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="12"/>
       <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -2197,15 +2261,16 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="13"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -2215,15 +2280,16 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="13"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -2233,21 +2299,22 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>105</v>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="H31" s="2"/>
-      <c r="I31" s="13"/>
+      <c r="I31" s="12"/>
       <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -2257,15 +2324,16 @@
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="19"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="13"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -2275,23 +2343,24 @@
       <c r="C33" s="2">
         <v>2301301026</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>109</v>
+      <c r="E33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="13"/>
+      <c r="I33" s="12"/>
       <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -2301,109 +2370,118 @@
       <c r="C34" s="2">
         <v>2301301072</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34" s="15" t="s">
+      <c r="E34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="H34" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I34" s="13"/>
+      <c r="I34" s="12"/>
       <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>35</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="41" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="2">
         <v>2301301028</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>73</v>
+      <c r="E35" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="13"/>
       <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>36</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="41" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27" t="s">
-        <v>75</v>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="13"/>
+      <c r="G36" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="12"/>
       <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>37</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="44" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="13"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="12"/>
       <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>74</v>
+      <c r="B38" s="40" t="s">
+        <v>73</v>
       </c>
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="13"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="12"/>
       <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2413,21 +2491,22 @@
       <c r="C39" s="2">
         <v>2301301006</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>77</v>
+      <c r="E39" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G39" s="16"/>
+        <v>84</v>
+      </c>
+      <c r="G39" s="15"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="13"/>
+      <c r="I39" s="12"/>
       <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2437,21 +2516,22 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27" t="s">
-        <v>97</v>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22" t="s">
+        <v>95</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I40" s="13"/>
+      <c r="G40" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I40" s="12"/>
       <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2461,217 +2541,244 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="13"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="12"/>
       <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="13"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="12"/>
       <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="37" t="s">
+      <c r="D43" s="22"/>
+      <c r="E43" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2301301022</v>
+      </c>
+      <c r="D44" s="46"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2301301009</v>
+      </c>
+      <c r="D45" s="46"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2301301080</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="3">
-        <v>2301301022</v>
-      </c>
-      <c r="D44" s="22"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>43</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2301301080</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="H46" s="2"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="2">
         <v>2301301090</v>
       </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+      <c r="D47" s="5"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="2">
+      <c r="B48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="2">
         <v>2301301015</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
     </row>
     <row r="57" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
     </row>
     <row r="58" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
     </row>
     <row r="59" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
     </row>
     <row r="60" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
     </row>
     <row r="61" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
     </row>
     <row r="62" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
     </row>
     <row r="63" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="G45:G47"/>
+  <mergeCells count="54">
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2688,26 +2795,24 @@
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H36:H37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2716,36 +2821,505 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83C6394-8E0F-4263-A0CC-51C895E48078}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr defaultRowHeight="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="49.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="3">
+    <row r="1" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1">
-        <v>2301301001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="C2">
-        <v>2301301005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67B9875-E30E-40AA-BC3A-CBF87DA6145B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F674DBF-8C6D-4FEF-914A-63A14186DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="118">
   <si>
     <t>S.No</t>
   </si>
@@ -442,7 +442,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,6 +500,72 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -625,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -652,6 +718,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,10 +746,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -701,21 +777,65 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1629,10 +1749,10 @@
       <c r="I1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="16" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1646,17 +1766,17 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="34" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I2" s="12"/>
@@ -1664,33 +1784,33 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
+      <c r="A3" s="31">
         <v>2</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="35">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="17"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="24"/>
       <c r="I3" s="12"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="25"/>
       <c r="I4" s="12"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1761,19 +1881,19 @@
       <c r="C7" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I7" s="12"/>
@@ -1790,11 +1910,11 @@
       <c r="C8" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="12"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1809,11 +1929,11 @@
       <c r="C9" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
       <c r="I9" s="12"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1828,17 +1948,17 @@
       <c r="C10" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="D10" s="29"/>
+      <c r="E10" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="26" t="s">
         <v>107</v>
       </c>
       <c r="I10" s="12"/>
@@ -1855,11 +1975,11 @@
       <c r="C11" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="20"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="27"/>
       <c r="I11" s="12"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1874,11 +1994,11 @@
       <c r="C12" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="21"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="28"/>
       <c r="I12" s="12"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -1991,7 +2111,7 @@
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="2">
@@ -2026,17 +2146,17 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22" t="s">
+      <c r="D18" s="29"/>
+      <c r="E18" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F18" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I18" s="12"/>
@@ -2053,11 +2173,11 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
       <c r="I19" s="12"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2072,11 +2192,11 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="12"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2098,25 +2218,25 @@
       <c r="A22" s="2">
         <v>22</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="23" t="s">
         <v>103</v>
       </c>
       <c r="I22" s="12"/>
@@ -2127,17 +2247,17 @@
       <c r="A23" s="2">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="18" t="s">
         <v>83</v>
       </c>
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
       <c r="I23" s="12"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2146,17 +2266,17 @@
       <c r="A24" s="2">
         <v>24</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="21" t="s">
         <v>65</v>
       </c>
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
       <c r="I24" s="12"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2171,17 +2291,17 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="43" t="s">
         <v>101</v>
       </c>
       <c r="G25" s="15"/>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I25" s="12"/>
@@ -2198,11 +2318,11 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="36"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="44"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="17"/>
+      <c r="H26" s="24"/>
       <c r="I26" s="12"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -2217,11 +2337,11 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="37"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="15"/>
-      <c r="H27" s="18"/>
+      <c r="H27" s="25"/>
       <c r="I27" s="12"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -2230,21 +2350,21 @@
       <c r="A28" s="2">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="21" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22" t="s">
+      <c r="D28" s="29"/>
+      <c r="E28" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="34" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I28" s="12"/>
@@ -2255,17 +2375,17 @@
       <c r="A29" s="2">
         <v>29</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="21" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="34"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="32"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="17"/>
+      <c r="H29" s="24"/>
       <c r="I29" s="12"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -2274,17 +2394,17 @@
       <c r="A30" s="2">
         <v>30</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="24"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="18"/>
+      <c r="H30" s="25"/>
       <c r="I30" s="12"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -2299,14 +2419,14 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22" t="s">
+      <c r="D31" s="29"/>
+      <c r="E31" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="23" t="s">
         <v>103</v>
       </c>
       <c r="H31" s="2"/>
@@ -2318,16 +2438,16 @@
       <c r="A32" s="2">
         <v>32</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="21" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="18"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="25"/>
       <c r="H32" s="2"/>
       <c r="I32" s="12"/>
       <c r="J32" s="2"/>
@@ -2337,7 +2457,7 @@
       <c r="A33" s="2">
         <v>33</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="2">
@@ -2364,7 +2484,7 @@
       <c r="A34" s="2">
         <v>34</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="47" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="2">
@@ -2393,7 +2513,7 @@
       <c r="A35" s="2">
         <v>35</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="2">
@@ -2422,21 +2542,21 @@
       <c r="A36" s="2">
         <v>36</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22" t="s">
+      <c r="D36" s="29"/>
+      <c r="E36" s="29" t="s">
         <v>74</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I36" s="12"/>
@@ -2447,17 +2567,17 @@
       <c r="A37" s="2">
         <v>37</v>
       </c>
-      <c r="B37" s="44" t="s">
+      <c r="B37" s="19" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="18"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="25"/>
       <c r="I37" s="12"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2466,16 +2586,16 @@
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="22" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="18"/>
+      <c r="G38" s="25"/>
       <c r="H38" s="15"/>
       <c r="I38" s="12"/>
       <c r="J38" s="2"/>
@@ -2510,21 +2630,21 @@
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="21" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22" t="s">
+      <c r="D40" s="29"/>
+      <c r="E40" s="29" t="s">
         <v>95</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="23" t="s">
         <v>103</v>
       </c>
       <c r="I40" s="12"/>
@@ -2535,17 +2655,17 @@
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
       <c r="I41" s="12"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -2554,17 +2674,17 @@
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
       <c r="I42" s="12"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2573,20 +2693,20 @@
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="23" t="s">
+      <c r="D43" s="29"/>
+      <c r="E43" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="42" t="s">
+      <c r="F43" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="23" t="s">
         <v>103</v>
       </c>
       <c r="H43" s="2"/>
@@ -2598,16 +2718,16 @@
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="2">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="17"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="24"/>
       <c r="H44" s="2"/>
       <c r="I44" s="12"/>
       <c r="J44" s="2"/>
@@ -2617,16 +2737,16 @@
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="18" t="s">
         <v>113</v>
       </c>
       <c r="C45" s="2">
         <v>2301301009</v>
       </c>
-      <c r="D45" s="46"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="21"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="28"/>
       <c r="H45" s="2"/>
       <c r="I45" s="12"/>
       <c r="J45" s="2"/>
@@ -2643,11 +2763,11 @@
         <v>2301301080</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="29" t="s">
         <v>58</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="23" t="s">
         <v>105</v>
       </c>
       <c r="H46" s="2"/>
@@ -2666,9 +2786,9 @@
         <v>2301301090</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="22"/>
+      <c r="E47" s="29"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="17"/>
+      <c r="G47" s="24"/>
       <c r="H47" s="2"/>
       <c r="I47" s="12"/>
       <c r="J47" s="2"/>
@@ -2685,9 +2805,9 @@
         <v>2301301015</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="22"/>
+      <c r="E48" s="29"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="18"/>
+      <c r="G48" s="25"/>
       <c r="H48" s="2"/>
       <c r="I48" s="12"/>
       <c r="J48" s="2"/>
@@ -2821,7 +2941,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83C6394-8E0F-4263-A0CC-51C895E48078}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -2832,219 +2952,289 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="20" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="74">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="74">
+        <v>2301301059</v>
+      </c>
+      <c r="D2" s="75"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
     </row>
     <row r="3" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="80">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="B3" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="77">
+        <v>2301301045</v>
+      </c>
+      <c r="D3" s="51"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
     </row>
     <row r="4" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="81"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="82">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="B5" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="82">
+        <v>2301301014</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="83">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="B6" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="83">
+        <v>2301301008</v>
+      </c>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="84">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="B7" s="84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="84">
+        <v>2301301068</v>
+      </c>
+      <c r="D7" s="85"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="84">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="B8" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="84">
+        <v>2301301069</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="84">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="B9" s="84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="84">
+        <v>2301301054</v>
+      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="69">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="B10" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="69">
+        <v>2301301004</v>
+      </c>
+      <c r="D10" s="70"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+    </row>
+    <row r="11" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="69">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="B11" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="69">
+        <v>2301301042</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="69">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="B12" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="69">
+        <v>2301301053</v>
+      </c>
+      <c r="D12" s="48"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+    </row>
+    <row r="13" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="86">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="B13" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="86">
+        <v>2301301020</v>
+      </c>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="B14" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="72">
+        <v>2301301027</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+    </row>
+    <row r="15" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="58">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="B15" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="58">
+        <v>2301301097</v>
+      </c>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+    </row>
+    <row r="16" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="87">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="B16" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="87">
+        <v>2301301023</v>
+      </c>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+    </row>
+    <row r="17" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="88">
         <v>15</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="B17" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="88">
+        <v>2301301029</v>
+      </c>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88">
+        <v>6</v>
+      </c>
+      <c r="F17" s="88"/>
+    </row>
+    <row r="18" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="82">
         <v>16</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="B18" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="82">
+        <v>2301301077</v>
+      </c>
+      <c r="D18" s="89"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+    </row>
+    <row r="19" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="82">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="B19" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="82">
+        <v>2301301046</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+    </row>
+    <row r="20" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="82">
         <v>18</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="B20" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="82">
+        <v>2301301058</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
     </row>
     <row r="21" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -3052,276 +3242,454 @@
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="52">
+        <v>19</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="52">
+        <v>2301301010</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="52">
+        <v>9</v>
+      </c>
+      <c r="F22" s="52"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="52">
+        <v>20</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="52">
+        <v>2301301002</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="52">
+        <v>10</v>
+      </c>
+      <c r="F23" s="52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="52">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="B24" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="52">
+        <v>2301301096</v>
+      </c>
+      <c r="D24" s="56"/>
+      <c r="E24" s="52">
+        <v>9</v>
+      </c>
+      <c r="F24" s="52"/>
+    </row>
+    <row r="25" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="74">
         <v>22</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="B25" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="74">
+        <v>2301301085</v>
+      </c>
+      <c r="D25" s="75"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+    </row>
+    <row r="26" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="74">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="B26" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="74">
+        <v>2401301135</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+    </row>
+    <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="74">
         <v>24</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="B27" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="74">
+        <v>2401301172</v>
+      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+    </row>
+    <row r="28" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="57">
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="B28" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="57">
+        <v>2301301016</v>
+      </c>
+      <c r="D28" s="64"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+    </row>
+    <row r="29" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="57">
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="B29" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="57">
+        <v>2301301034</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="57">
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="B30" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="57">
+        <v>2301301030</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="71">
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="B31" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="71">
+        <v>2301301082</v>
+      </c>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+    </row>
+    <row r="32" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="71">
         <v>29</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="B32" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="71">
+        <v>2301301110</v>
+      </c>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71">
+        <v>8</v>
+      </c>
+      <c r="F32" s="71"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58">
         <v>30</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="B33" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="58">
+        <v>2301301026</v>
+      </c>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58">
+        <v>6</v>
+      </c>
+      <c r="F33" s="58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="72">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="B34" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="72">
+        <v>2301301072</v>
+      </c>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72">
+        <v>9</v>
+      </c>
+      <c r="F34" s="72"/>
     </row>
     <row r="35" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2301301028</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2">
+        <v>8</v>
+      </c>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="59">
+        <v>33</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="59">
+        <v>2301301109</v>
+      </c>
+      <c r="D36" s="63"/>
+      <c r="E36" s="59">
+        <v>9</v>
+      </c>
+      <c r="F36" s="59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="59">
         <v>34</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="B37" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="59">
+        <v>2301301074</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="59">
+        <v>8</v>
+      </c>
+      <c r="F37" s="59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="59">
         <v>35</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="B38" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="59">
+        <v>2301301011</v>
+      </c>
+      <c r="D38" s="48"/>
+      <c r="E38" s="59">
+        <v>7</v>
+      </c>
+      <c r="F38" s="59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="84">
         <v>36</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="B39" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="84">
+        <v>2301301006</v>
+      </c>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+    </row>
+    <row r="40" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="58">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="B40" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="58">
+        <v>2301301018</v>
+      </c>
+      <c r="D40" s="65"/>
+      <c r="E40" s="58">
+        <v>7</v>
+      </c>
+      <c r="F40" s="58"/>
+    </row>
+    <row r="41" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="58">
         <v>38</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="B41" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="58">
+        <v>2301301021</v>
+      </c>
+      <c r="D41" s="51"/>
+      <c r="E41" s="58">
+        <v>7</v>
+      </c>
+      <c r="F41" s="58"/>
+    </row>
+    <row r="42" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="58">
         <v>39</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="B42" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="58">
+        <v>2301301005</v>
+      </c>
+      <c r="D42" s="48"/>
+      <c r="E42" s="58">
+        <v>7</v>
+      </c>
+      <c r="F42" s="58"/>
+    </row>
+    <row r="43" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
         <v>40</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="B43" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="10">
+        <v>2301301102</v>
+      </c>
+      <c r="D43" s="68"/>
+      <c r="E43" s="10">
+        <v>9</v>
+      </c>
+      <c r="F43" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10">
         <v>41</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="B44" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="10">
+        <v>2301301022</v>
+      </c>
+      <c r="D44" s="51"/>
+      <c r="E44" s="10">
+        <v>7</v>
+      </c>
+      <c r="F44" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10">
         <v>42</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="B45" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="10">
+        <v>2301301009</v>
+      </c>
+      <c r="D45" s="48"/>
+      <c r="E45" s="10">
+        <v>8</v>
+      </c>
+      <c r="F45" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="69">
         <v>43</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="B46" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="69">
+        <v>2301301080</v>
+      </c>
+      <c r="D46" s="70"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+    </row>
+    <row r="47" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="69">
         <v>44</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="B47" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="69">
+        <v>2301301090</v>
+      </c>
+      <c r="D47" s="51"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+    </row>
+    <row r="48" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="69">
         <v>45</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+      <c r="B48" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="69">
+        <v>2301301015</v>
+      </c>
+      <c r="D48" s="48"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+    </row>
+    <row r="49" spans="2:2" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="50"/>
+    </row>
+    <row r="50" spans="2:2" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="50"/>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D28:D30"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F674DBF-8C6D-4FEF-914A-63A14186DEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDD99D6-2397-46EE-A4B0-74B41D96FA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BTech 6th Sem Attendance" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="119">
   <si>
     <t>S.No</t>
   </si>
@@ -184,9 +184,6 @@
   </si>
   <si>
     <t>Solo</t>
-  </si>
-  <si>
-    <t>Car Pooling App</t>
   </si>
   <si>
     <t>Versionrisers</t>
@@ -390,6 +387,12 @@
   </si>
   <si>
     <t>Viva</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>A+</t>
   </si>
 </sst>
 </file>
@@ -691,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -725,6 +728,59 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -734,29 +790,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -777,65 +824,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1738,22 +1754,22 @@
         <v>50</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>98</v>
-      </c>
       <c r="I1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1766,252 +1782,250 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>81</v>
+      <c r="D2" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>80</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="23" t="s">
-        <v>107</v>
+      <c r="H2" s="64" t="s">
+        <v>106</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31">
+      <c r="A3" s="74">
         <v>2</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="72">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="24"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="65"/>
       <c r="I3" s="12"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="25"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="66"/>
       <c r="I4" s="12"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2">
-        <v>2301301014</v>
+        <v>2301301008</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>103</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="12"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2">
-        <v>2301301008</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="5" t="s">
+        <v>2301301068</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2"/>
       <c r="I6" s="12"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2">
-        <v>2301301068</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>107</v>
-      </c>
+        <v>2301301069</v>
+      </c>
+      <c r="D7" s="71"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="12"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2">
-        <v>2301301069</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+        <v>2301301054</v>
+      </c>
+      <c r="D8" s="71"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
       <c r="I8" s="12"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2">
-        <v>2301301054</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+        <v>2301301004</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>106</v>
+      </c>
       <c r="I9" s="12"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2">
-        <v>2301301004</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>107</v>
-      </c>
+        <v>2301301042</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="12"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2">
-        <v>2301301042</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="27"/>
+        <v>2301301053</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="82"/>
       <c r="I11" s="12"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2">
-        <v>2301301053</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="28"/>
+        <v>2301301020</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="85" t="s">
+        <v>106</v>
+      </c>
       <c r="I12" s="12"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2">
-        <v>2301301020</v>
+        <v>2301301027</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>53</v>
@@ -2020,9 +2034,11 @@
         <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="15"/>
+        <v>80</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="12"/>
       <c r="J13" s="2"/>
@@ -2030,13 +2046,13 @@
     </row>
     <row r="14" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>2301301027</v>
+        <v>2301301097</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>53</v>
@@ -2045,11 +2061,9 @@
         <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>107</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G14" s="15"/>
       <c r="H14" s="2"/>
       <c r="I14" s="12"/>
       <c r="J14" s="2"/>
@@ -2057,81 +2071,75 @@
     </row>
     <row r="15" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
-        <v>2301301097</v>
+        <v>2301301023</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="85" t="s">
+        <v>106</v>
+      </c>
       <c r="I15" s="12"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="2">
-        <v>2301301023</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>2301301029</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>118</v>
+      </c>
       <c r="I16" s="12"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>64</v>
+      <c r="A17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C17" s="2">
-        <v>2301301029</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>107</v>
-      </c>
+        <v>2301301014</v>
+      </c>
+      <c r="D17" s="75"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
       <c r="I17" s="12"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2146,18 +2154,18 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>107</v>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>118</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="2"/>
@@ -2173,11 +2181,11 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
       <c r="I19" s="12"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2192,11 +2200,11 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
       <c r="I20" s="12"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2224,20 +2232,20 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>103</v>
+      <c r="F22" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="64" t="s">
+        <v>102</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="2"/>
@@ -2248,16 +2256,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
       <c r="I23" s="12"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2267,16 +2275,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
       <c r="I24" s="12"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2291,18 +2299,18 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="43" t="s">
+      <c r="D25" s="71" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="79" t="s">
         <v>101</v>
       </c>
+      <c r="F25" s="48" t="s">
+        <v>100</v>
+      </c>
       <c r="G25" s="15"/>
-      <c r="H25" s="23" t="s">
-        <v>107</v>
+      <c r="H25" s="64" t="s">
+        <v>106</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="2"/>
@@ -2318,11 +2326,11 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="44"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="68"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="24"/>
+      <c r="H26" s="65"/>
       <c r="I26" s="12"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -2337,11 +2345,11 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="45"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="69"/>
       <c r="G27" s="15"/>
-      <c r="H27" s="25"/>
+      <c r="H27" s="66"/>
       <c r="I27" s="12"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -2356,16 +2364,16 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>82</v>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="67" t="s">
+        <v>81</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="H28" s="23" t="s">
-        <v>107</v>
+      <c r="H28" s="64" t="s">
+        <v>106</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="2"/>
@@ -2381,11 +2389,11 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="32"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="46"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="24"/>
+      <c r="H29" s="65"/>
       <c r="I29" s="12"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -2400,11 +2408,11 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="33"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="47"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="66"/>
       <c r="I30" s="12"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -2419,15 +2427,15 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>103</v>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="64" t="s">
+        <v>102</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="12"/>
@@ -2439,15 +2447,15 @@
         <v>32</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="25"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="66"/>
       <c r="H32" s="2"/>
       <c r="I32" s="12"/>
       <c r="J32" s="2"/>
@@ -2467,13 +2475,13 @@
         <v>53</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="12"/>
@@ -2484,7 +2492,7 @@
       <c r="A34" s="2">
         <v>34</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="2">
@@ -2494,16 +2502,16 @@
         <v>53</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="2"/>
@@ -2523,17 +2531,17 @@
         <v>53</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -2548,16 +2556,16 @@
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29" t="s">
-        <v>74</v>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71" t="s">
+        <v>73</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>107</v>
+      <c r="G36" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="64" t="s">
+        <v>106</v>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="2"/>
@@ -2573,11 +2581,11 @@
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="25"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="66"/>
       <c r="I37" s="12"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2587,15 +2595,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="25"/>
+      <c r="G38" s="66"/>
       <c r="H38" s="15"/>
       <c r="I38" s="12"/>
       <c r="J38" s="2"/>
@@ -2615,10 +2623,10 @@
         <v>53</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="2"/>
@@ -2636,16 +2644,16 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29" t="s">
-        <v>95</v>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71" t="s">
+        <v>94</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" s="23" t="s">
+      <c r="G40" s="64" t="s">
         <v>103</v>
+      </c>
+      <c r="H40" s="64" t="s">
+        <v>102</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="2"/>
@@ -2661,11 +2669,11 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
       <c r="I41" s="12"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -2675,16 +2683,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
       <c r="I42" s="12"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2699,15 +2707,15 @@
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F43" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>103</v>
+      <c r="D43" s="71"/>
+      <c r="E43" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="64" t="s">
+        <v>102</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="12"/>
@@ -2719,15 +2727,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="24"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="2"/>
       <c r="I44" s="12"/>
       <c r="J44" s="2"/>
@@ -2738,15 +2746,15 @@
         <v>44</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2">
         <v>2301301009</v>
       </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="28"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="82"/>
       <c r="H45" s="2"/>
       <c r="I45" s="12"/>
       <c r="J45" s="2"/>
@@ -2763,14 +2771,16 @@
         <v>2301301080</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="29" t="s">
-        <v>58</v>
+      <c r="E46" s="71" t="s">
+        <v>57</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H46" s="2"/>
+      <c r="G46" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="H46" s="88" t="s">
+        <v>106</v>
+      </c>
       <c r="I46" s="12"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -2780,16 +2790,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C47" s="2">
         <v>2301301090</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="29"/>
+      <c r="E47" s="71"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="2"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="89"/>
       <c r="I47" s="12"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -2799,16 +2809,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" s="2">
         <v>2301301015</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="29"/>
+      <c r="E48" s="71"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="2"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="90"/>
       <c r="I48" s="12"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -2878,27 +2888,31 @@
       <c r="E64" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
+  <mergeCells count="60">
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2910,29 +2924,31 @@
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="E25:E27"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="G18:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2941,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83C6394-8E0F-4263-A0CC-51C895E48078}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
@@ -2953,7 +2969,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>1</v>
@@ -2962,276 +2978,276 @@
         <v>2</v>
       </c>
       <c r="D1" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="2" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="74">
+      <c r="C2" s="38">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="80">
+      <c r="A3" s="57">
         <v>2</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="77">
+      <c r="C3" s="55">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="81"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
     </row>
     <row r="5" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82">
+      <c r="A5" s="39">
         <v>3</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="82">
+      <c r="C5" s="39">
         <v>2301301014</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83">
+      <c r="A6" s="40">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="40">
         <v>2301301008</v>
       </c>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="84">
+      <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="41">
+        <v>2301301068</v>
+      </c>
+      <c r="D7" s="51"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="41">
+        <v>6</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="41">
+        <v>2301301069</v>
+      </c>
+      <c r="D8" s="46"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="41">
+        <v>7</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="41">
+        <v>2301301054</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="34">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="34">
+        <v>2301301004</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="34">
+        <v>9</v>
+      </c>
+      <c r="B11" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="84">
-        <v>2301301068</v>
-      </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="84">
+      <c r="C11" s="34">
+        <v>2301301042</v>
+      </c>
+      <c r="D11" s="46"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="34">
+        <v>10</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="34">
+        <v>2301301053</v>
+      </c>
+      <c r="D12" s="47"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="42">
+        <v>11</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="42">
+        <v>2301301020</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36">
+        <v>12</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="36">
+        <v>2301301027</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+    </row>
+    <row r="15" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
+        <v>13</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="27">
+        <v>2301301097</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+    </row>
+    <row r="16" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="43">
+        <v>14</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="43">
+        <v>2301301023</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="44">
+        <v>15</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="44">
+        <v>2301301029</v>
+      </c>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44">
         <v>6</v>
       </c>
-      <c r="B8" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="84">
-        <v>2301301069</v>
-      </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84">
-        <v>7</v>
-      </c>
-      <c r="B9" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="84">
-        <v>2301301054</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="69">
-        <v>8</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="69">
-        <v>2301301004</v>
-      </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69">
-        <v>9</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="69">
-        <v>2301301042</v>
-      </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="69">
-        <v>10</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="69">
-        <v>2301301053</v>
-      </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86">
-        <v>11</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="86">
-        <v>2301301020</v>
-      </c>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="72">
-        <v>12</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="72">
-        <v>2301301027</v>
-      </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58">
-        <v>13</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="58">
-        <v>2301301097</v>
-      </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87">
-        <v>14</v>
-      </c>
-      <c r="B16" s="87" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="87">
-        <v>2301301023</v>
-      </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88">
-        <v>15</v>
-      </c>
-      <c r="B17" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="88">
-        <v>2301301029</v>
-      </c>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88">
-        <v>6</v>
-      </c>
-      <c r="F17" s="88"/>
+      <c r="F17" s="44"/>
     </row>
     <row r="18" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82">
+      <c r="A18" s="39">
         <v>16</v>
       </c>
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="82">
+      <c r="C18" s="39">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="89"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
     </row>
     <row r="19" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82">
+      <c r="A19" s="39">
         <v>17</v>
       </c>
-      <c r="B19" s="82" t="s">
+      <c r="B19" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="82">
+      <c r="C19" s="39">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82">
+      <c r="A20" s="39">
         <v>18</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="82">
+      <c r="C20" s="39">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="48"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
@@ -3242,208 +3258,208 @@
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="52">
+      <c r="A22" s="24">
         <v>19</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="24">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="52">
+      <c r="D22" s="59"/>
+      <c r="E22" s="24">
         <v>9</v>
       </c>
-      <c r="F22" s="52"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52">
+      <c r="A23" s="24">
         <v>20</v>
       </c>
-      <c r="B23" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="52">
+      <c r="B23" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="24">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="55"/>
-      <c r="E23" s="52">
+      <c r="D23" s="60"/>
+      <c r="E23" s="24">
         <v>10</v>
       </c>
-      <c r="F23" s="52">
+      <c r="F23" s="24">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="52">
+      <c r="A24" s="24">
         <v>21</v>
       </c>
-      <c r="B24" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="52">
+      <c r="B24" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="24">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="52">
+      <c r="D24" s="61"/>
+      <c r="E24" s="24">
         <v>9</v>
       </c>
-      <c r="F24" s="52"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="74">
+      <c r="A25" s="38">
         <v>22</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="74">
+      <c r="C25" s="38">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="75"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="74">
+      <c r="A26" s="38">
         <v>23</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="74">
+      <c r="C26" s="38">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="74">
+      <c r="A27" s="38">
         <v>24</v>
       </c>
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="74">
+      <c r="C27" s="38">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="48"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
     </row>
     <row r="28" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="57">
+      <c r="A28" s="26">
         <v>25</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="26">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="57">
+      <c r="A29" s="26">
         <v>26</v>
       </c>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="26">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="57">
+      <c r="A30" s="26">
         <v>27</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="26">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="71">
+      <c r="A31" s="35">
         <v>28</v>
       </c>
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="71">
+      <c r="C31" s="35">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
     </row>
     <row r="32" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="71">
+      <c r="A32" s="35">
         <v>29</v>
       </c>
-      <c r="B32" s="71" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="71">
+      <c r="B32" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="35">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71">
+      <c r="D32" s="35"/>
+      <c r="E32" s="35">
         <v>8</v>
       </c>
-      <c r="F32" s="71"/>
+      <c r="F32" s="35"/>
     </row>
     <row r="33" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="58">
+      <c r="A33" s="27">
         <v>30</v>
       </c>
-      <c r="B33" s="58" t="s">
+      <c r="B33" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="58">
+      <c r="C33" s="27">
         <v>2301301026</v>
       </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58">
+      <c r="D33" s="27"/>
+      <c r="E33" s="27">
         <v>6</v>
       </c>
-      <c r="F33" s="58">
+      <c r="F33" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="72">
+      <c r="A34" s="36">
         <v>31</v>
       </c>
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="36">
         <v>2301301072</v>
       </c>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72">
+      <c r="D34" s="36"/>
+      <c r="E34" s="36">
         <v>9</v>
       </c>
-      <c r="F34" s="72"/>
+      <c r="F34" s="36"/>
     </row>
     <row r="35" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>32</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="2">
@@ -3456,132 +3472,132 @@
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="59">
+      <c r="A36" s="28">
         <v>33</v>
       </c>
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="28">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="63"/>
-      <c r="E36" s="59">
+      <c r="D36" s="62"/>
+      <c r="E36" s="28">
         <v>9</v>
       </c>
-      <c r="F36" s="59">
+      <c r="F36" s="28">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="59">
+      <c r="A37" s="28">
         <v>34</v>
       </c>
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="28">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="51"/>
-      <c r="E37" s="59">
+      <c r="D37" s="46"/>
+      <c r="E37" s="28">
         <v>8</v>
       </c>
-      <c r="F37" s="59">
+      <c r="F37" s="28">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="59">
+      <c r="A38" s="28">
         <v>35</v>
       </c>
-      <c r="B38" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="59">
+      <c r="B38" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="28">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="48"/>
-      <c r="E38" s="59">
+      <c r="D38" s="47"/>
+      <c r="E38" s="28">
         <v>7</v>
       </c>
-      <c r="F38" s="59">
+      <c r="F38" s="28">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="84">
+      <c r="A39" s="41">
         <v>36</v>
       </c>
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="84">
+      <c r="C39" s="41">
         <v>2301301006</v>
       </c>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
     </row>
     <row r="40" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="58">
+      <c r="A40" s="27">
         <v>37</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="58">
+      <c r="C40" s="27">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="58">
+      <c r="D40" s="45"/>
+      <c r="E40" s="27">
         <v>7</v>
       </c>
-      <c r="F40" s="58"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="58">
+      <c r="A41" s="27">
         <v>38</v>
       </c>
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="58">
+      <c r="C41" s="27">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="51"/>
-      <c r="E41" s="58">
+      <c r="D41" s="46"/>
+      <c r="E41" s="27">
         <v>7</v>
       </c>
-      <c r="F41" s="58"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="58">
+      <c r="A42" s="27">
         <v>39</v>
       </c>
-      <c r="B42" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="58">
+      <c r="B42" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="27">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="58">
+      <c r="D42" s="47"/>
+      <c r="E42" s="27">
         <v>7</v>
       </c>
-      <c r="F42" s="58"/>
+      <c r="F42" s="27"/>
     </row>
     <row r="43" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>40</v>
       </c>
-      <c r="B43" s="66" t="s">
+      <c r="B43" s="32" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="10">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="68"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="10">
         <v>9</v>
       </c>
@@ -3593,13 +3609,13 @@
       <c r="A44" s="10">
         <v>41</v>
       </c>
-      <c r="B44" s="67" t="s">
-        <v>70</v>
+      <c r="B44" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="C44" s="10">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="51"/>
+      <c r="D44" s="46"/>
       <c r="E44" s="10">
         <v>7</v>
       </c>
@@ -3611,13 +3627,13 @@
       <c r="A45" s="10">
         <v>42</v>
       </c>
-      <c r="B45" s="66" t="s">
-        <v>113</v>
+      <c r="B45" s="32" t="s">
+        <v>112</v>
       </c>
       <c r="C45" s="10">
         <v>2301301009</v>
       </c>
-      <c r="D45" s="48"/>
+      <c r="D45" s="47"/>
       <c r="E45" s="10">
         <v>8</v>
       </c>
@@ -3626,55 +3642,55 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="69">
+      <c r="A46" s="34">
         <v>43</v>
       </c>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="69">
+      <c r="C46" s="34">
         <v>2301301080</v>
       </c>
-      <c r="D46" s="70"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
     </row>
     <row r="47" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="69">
+      <c r="A47" s="34">
         <v>44</v>
       </c>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="34">
+        <v>2301301090</v>
+      </c>
+      <c r="D47" s="46"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+    </row>
+    <row r="48" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="34">
+        <v>45</v>
+      </c>
+      <c r="B48" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="69">
-        <v>2301301090</v>
-      </c>
-      <c r="D47" s="51"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-    </row>
-    <row r="48" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="69">
-        <v>45</v>
-      </c>
-      <c r="B48" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="69">
+      <c r="C48" s="34">
         <v>2301301015</v>
       </c>
-      <c r="D48" s="48"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-    </row>
-    <row r="49" spans="2:2" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="50"/>
-    </row>
-    <row r="50" spans="2:2" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="50"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D28:D30"/>
     <mergeCell ref="D40:D42"/>
     <mergeCell ref="D43:D45"/>
     <mergeCell ref="D46:D48"/>
@@ -3683,12 +3699,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D28:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Btech_Project/BTech_6th_Sem_Student_List.xlsx
+++ b/Btech_Project/BTech_6th_Sem_Student_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Geeta\Btech_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDD99D6-2397-46EE-A4B0-74B41D96FA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C1BA1F-814B-4AE5-898C-5322BC6DC068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="119">
   <si>
     <t>S.No</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>Lost-Found Items Managemt in campus - MERN</t>
-  </si>
-  <si>
-    <t>"Charity GPT" - Place to find correct charities org.</t>
   </si>
   <si>
     <t>Tejasvi sharma</t>
@@ -394,12 +391,15 @@
   <si>
     <t>A+</t>
   </si>
+  <si>
+    <t>ERP - Smart Learning &amp; breaking Language barrier</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,6 +440,19 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -694,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -750,37 +763,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -791,11 +776,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -824,8 +815,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -834,7 +830,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -843,15 +845,43 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1754,22 +1784,22 @@
         <v>50</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>97</v>
-      </c>
       <c r="I1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1782,51 +1812,51 @@
       <c r="C2" s="2">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>80</v>
+      <c r="D2" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>79</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="64" t="s">
-        <v>106</v>
+      <c r="H2" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74">
+      <c r="A3" s="60">
         <v>2</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="72">
+      <c r="C3" s="58">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="65"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="47"/>
       <c r="I3" s="12"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="66"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="12"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1845,13 +1875,13 @@
         <v>53</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="12"/>
@@ -1868,20 +1898,20 @@
       <c r="C6" s="2">
         <v>2301301068</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="64" t="s">
-        <v>106</v>
+      <c r="G6" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="67" t="s">
+        <v>105</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="2"/>
@@ -1897,11 +1927,11 @@
       <c r="C7" s="2">
         <v>2301301069</v>
       </c>
-      <c r="D7" s="71"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="68"/>
       <c r="I7" s="12"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1916,11 +1946,11 @@
       <c r="C8" s="2">
         <v>2301301054</v>
       </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="69"/>
       <c r="I8" s="12"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1935,18 +1965,18 @@
       <c r="C9" s="2">
         <v>2301301004</v>
       </c>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71" t="s">
+      <c r="D9" s="56"/>
+      <c r="E9" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="83" t="s">
-        <v>106</v>
+      <c r="F9" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="70" t="s">
+        <v>105</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9" s="2"/>
@@ -1962,11 +1992,11 @@
       <c r="C10" s="2">
         <v>2301301042</v>
       </c>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="84"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="71"/>
       <c r="I10" s="12"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1981,11 +2011,11 @@
       <c r="C11" s="2">
         <v>2301301053</v>
       </c>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="82"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="57"/>
       <c r="I11" s="12"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2007,11 +2037,11 @@
         <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="15"/>
-      <c r="H12" s="85" t="s">
-        <v>106</v>
+      <c r="H12" s="45" t="s">
+        <v>105</v>
       </c>
       <c r="I12" s="12"/>
       <c r="J12" s="2"/>
@@ -2034,47 +2064,49 @@
         <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="12"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="14" spans="1:11" s="95" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="97">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="97">
         <v>2301301097</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="E14" s="98" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="94"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="99" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>2301301023</v>
@@ -2083,16 +2115,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="G15" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="85" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>105</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="2"/>
@@ -2103,23 +2135,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>2301301029</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="83" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="64" t="s">
-        <v>118</v>
+      <c r="D16" s="60"/>
+      <c r="E16" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="75" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>117</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="2"/>
@@ -2127,7 +2159,7 @@
     </row>
     <row r="17" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -2135,11 +2167,11 @@
       <c r="C17" s="2">
         <v>2301301014</v>
       </c>
-      <c r="D17" s="75"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="12"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2154,18 +2186,18 @@
       <c r="C18" s="2">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="F18" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="64" t="s">
-        <v>118</v>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>117</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="2"/>
@@ -2181,11 +2213,11 @@
       <c r="C19" s="2">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="12"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2200,11 +2232,11 @@
       <c r="C20" s="2">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="12"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2232,20 +2264,20 @@
       <c r="C22" s="2">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="71" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="H22" s="64" t="s">
-        <v>102</v>
+      <c r="F22" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="2"/>
@@ -2256,16 +2288,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
       <c r="I23" s="12"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2275,16 +2307,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="12"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2299,18 +2331,18 @@
       <c r="C25" s="2">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="71" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="48" t="s">
+      <c r="D25" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="65" t="s">
         <v>100</v>
       </c>
+      <c r="F25" s="52" t="s">
+        <v>99</v>
+      </c>
       <c r="G25" s="15"/>
-      <c r="H25" s="64" t="s">
-        <v>106</v>
+      <c r="H25" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="2"/>
@@ -2326,11 +2358,11 @@
       <c r="C26" s="2">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="68"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="53"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="65"/>
+      <c r="H26" s="47"/>
       <c r="I26" s="12"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -2345,11 +2377,11 @@
       <c r="C27" s="2">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="69"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="54"/>
       <c r="G27" s="15"/>
-      <c r="H27" s="66"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="12"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -2364,16 +2396,16 @@
       <c r="C28" s="2">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" s="67" t="s">
-        <v>81</v>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>80</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="H28" s="64" t="s">
-        <v>106</v>
+      <c r="H28" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="2"/>
@@ -2389,11 +2421,11 @@
       <c r="C29" s="2">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="46"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="50"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="65"/>
+      <c r="H29" s="47"/>
       <c r="I29" s="12"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -2408,11 +2440,11 @@
       <c r="C30" s="2">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="47"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="51"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="66"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="12"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -2427,15 +2459,15 @@
       <c r="C31" s="2">
         <v>2301301082</v>
       </c>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" s="64" t="s">
-        <v>102</v>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="12"/>
@@ -2447,15 +2479,15 @@
         <v>32</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" s="2">
         <v>2301301110</v>
       </c>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="66"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="48"/>
       <c r="H32" s="2"/>
       <c r="I32" s="12"/>
       <c r="J32" s="2"/>
@@ -2475,13 +2507,13 @@
         <v>53</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="12"/>
@@ -2502,16 +2534,16 @@
         <v>53</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="2"/>
@@ -2531,17 +2563,17 @@
         <v>53</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="12" t="s">
-        <v>106</v>
+      <c r="I35" s="96" t="s">
+        <v>105</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -2556,16 +2588,16 @@
       <c r="C36" s="2">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71" t="s">
-        <v>73</v>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56" t="s">
+        <v>72</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="H36" s="64" t="s">
-        <v>106</v>
+      <c r="G36" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="H36" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="2"/>
@@ -2581,11 +2613,11 @@
       <c r="C37" s="2">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="66"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
       <c r="I37" s="12"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2595,15 +2627,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="66"/>
+      <c r="G38" s="48"/>
       <c r="H38" s="15"/>
       <c r="I38" s="12"/>
       <c r="J38" s="2"/>
@@ -2623,14 +2655,16 @@
         <v>53</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="12" t="s">
+        <v>101</v>
+      </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
@@ -2644,16 +2678,16 @@
       <c r="C40" s="2">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71" t="s">
-        <v>94</v>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56" t="s">
+        <v>93</v>
       </c>
       <c r="F40" s="2"/>
-      <c r="G40" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="H40" s="64" t="s">
+      <c r="G40" s="46" t="s">
         <v>102</v>
+      </c>
+      <c r="H40" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="2"/>
@@ -2669,11 +2703,11 @@
       <c r="C41" s="2">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
       <c r="I41" s="12"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -2683,16 +2717,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" s="2">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
       <c r="I42" s="12"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2707,15 +2741,15 @@
       <c r="C43" s="2">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="71"/>
-      <c r="E43" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43" s="64" t="s">
-        <v>102</v>
+      <c r="D43" s="56"/>
+      <c r="E43" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="12"/>
@@ -2727,15 +2761,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="2">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="81"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="65"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="47"/>
       <c r="H44" s="2"/>
       <c r="I44" s="12"/>
       <c r="J44" s="2"/>
@@ -2746,15 +2780,15 @@
         <v>44</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45" s="2">
         <v>2301301009</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="82"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="57"/>
       <c r="H45" s="2"/>
       <c r="I45" s="12"/>
       <c r="J45" s="2"/>
@@ -2771,15 +2805,15 @@
         <v>2301301080</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="71" t="s">
+      <c r="E46" s="56" t="s">
         <v>57</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="H46" s="88" t="s">
-        <v>106</v>
+      <c r="G46" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="72" t="s">
+        <v>105</v>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="2"/>
@@ -2790,16 +2824,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C47" s="2">
         <v>2301301090</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="71"/>
+      <c r="E47" s="56"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="89"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="73"/>
       <c r="I47" s="12"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -2809,16 +2843,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48" s="2">
         <v>2301301015</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="71"/>
+      <c r="E48" s="56"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="90"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="74"/>
       <c r="I48" s="12"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -2896,14 +2930,7 @@
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="H40:H42"/>
     <mergeCell ref="H28:H30"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="H18:H20"/>
     <mergeCell ref="H36:H37"/>
-    <mergeCell ref="H16:H17"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="G40:G42"/>
     <mergeCell ref="D40:D42"/>
@@ -2912,6 +2939,13 @@
     <mergeCell ref="D43:D45"/>
     <mergeCell ref="E43:E45"/>
     <mergeCell ref="F43:F45"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H16:H17"/>
     <mergeCell ref="G43:G45"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="A3:A4"/>
@@ -2969,7 +3003,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>1</v>
@@ -2978,13 +3012,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
         <v>115</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -2997,29 +3031,29 @@
       <c r="C2" s="38">
         <v>2301301059</v>
       </c>
-      <c r="D2" s="50"/>
+      <c r="D2" s="80"/>
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57">
+      <c r="A3" s="87">
         <v>2</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="85">
         <v>2301301045</v>
       </c>
-      <c r="D3" s="46"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="47"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="51"/>
       <c r="E4" s="38"/>
       <c r="F4" s="38"/>
     </row>
@@ -3061,7 +3095,7 @@
       <c r="C7" s="41">
         <v>2301301068</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="81"/>
       <c r="E7" s="41"/>
       <c r="F7" s="41"/>
     </row>
@@ -3075,7 +3109,7 @@
       <c r="C8" s="41">
         <v>2301301069</v>
       </c>
-      <c r="D8" s="46"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="41"/>
       <c r="F8" s="41"/>
     </row>
@@ -3089,7 +3123,7 @@
       <c r="C9" s="41">
         <v>2301301054</v>
       </c>
-      <c r="D9" s="47"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="41"/>
       <c r="F9" s="41"/>
     </row>
@@ -3103,7 +3137,7 @@
       <c r="C10" s="34">
         <v>2301301004</v>
       </c>
-      <c r="D10" s="49"/>
+      <c r="D10" s="79"/>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
     </row>
@@ -3117,7 +3151,7 @@
       <c r="C11" s="34">
         <v>2301301042</v>
       </c>
-      <c r="D11" s="46"/>
+      <c r="D11" s="50"/>
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
     </row>
@@ -3131,7 +3165,7 @@
       <c r="C12" s="34">
         <v>2301301053</v>
       </c>
-      <c r="D12" s="47"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
     </row>
@@ -3182,7 +3216,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="43">
         <v>2301301023</v>
@@ -3196,7 +3230,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="44">
         <v>2301301029</v>
@@ -3217,7 +3251,7 @@
       <c r="C18" s="39">
         <v>2301301077</v>
       </c>
-      <c r="D18" s="52"/>
+      <c r="D18" s="82"/>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
     </row>
@@ -3231,7 +3265,7 @@
       <c r="C19" s="39">
         <v>2301301046</v>
       </c>
-      <c r="D19" s="46"/>
+      <c r="D19" s="50"/>
       <c r="E19" s="39"/>
       <c r="F19" s="39"/>
     </row>
@@ -3245,7 +3279,7 @@
       <c r="C20" s="39">
         <v>2301301058</v>
       </c>
-      <c r="D20" s="47"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="39"/>
       <c r="F20" s="39"/>
     </row>
@@ -3267,7 +3301,7 @@
       <c r="C22" s="24">
         <v>2301301010</v>
       </c>
-      <c r="D22" s="59"/>
+      <c r="D22" s="89"/>
       <c r="E22" s="24">
         <v>9</v>
       </c>
@@ -3278,12 +3312,12 @@
         <v>20</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="24">
         <v>2301301002</v>
       </c>
-      <c r="D23" s="60"/>
+      <c r="D23" s="90"/>
       <c r="E23" s="24">
         <v>10</v>
       </c>
@@ -3296,12 +3330,12 @@
         <v>21</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="24">
         <v>2301301096</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="24">
         <v>9</v>
       </c>
@@ -3317,7 +3351,7 @@
       <c r="C25" s="38">
         <v>2301301085</v>
       </c>
-      <c r="D25" s="50"/>
+      <c r="D25" s="80"/>
       <c r="E25" s="38"/>
       <c r="F25" s="38"/>
     </row>
@@ -3331,7 +3365,7 @@
       <c r="C26" s="38">
         <v>2401301135</v>
       </c>
-      <c r="D26" s="46"/>
+      <c r="D26" s="50"/>
       <c r="E26" s="38"/>
       <c r="F26" s="38"/>
     </row>
@@ -3345,7 +3379,7 @@
       <c r="C27" s="38">
         <v>2401301172</v>
       </c>
-      <c r="D27" s="47"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="38"/>
       <c r="F27" s="38"/>
     </row>
@@ -3359,7 +3393,7 @@
       <c r="C28" s="26">
         <v>2301301016</v>
       </c>
-      <c r="D28" s="63"/>
+      <c r="D28" s="93"/>
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
     </row>
@@ -3373,7 +3407,7 @@
       <c r="C29" s="26">
         <v>2301301034</v>
       </c>
-      <c r="D29" s="46"/>
+      <c r="D29" s="50"/>
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
     </row>
@@ -3387,7 +3421,7 @@
       <c r="C30" s="26">
         <v>2301301030</v>
       </c>
-      <c r="D30" s="47"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
     </row>
@@ -3410,7 +3444,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" s="35">
         <v>2301301110</v>
@@ -3481,7 +3515,7 @@
       <c r="C36" s="28">
         <v>2301301109</v>
       </c>
-      <c r="D36" s="62"/>
+      <c r="D36" s="92"/>
       <c r="E36" s="28">
         <v>9</v>
       </c>
@@ -3499,7 +3533,7 @@
       <c r="C37" s="28">
         <v>2301301074</v>
       </c>
-      <c r="D37" s="46"/>
+      <c r="D37" s="50"/>
       <c r="E37" s="28">
         <v>8</v>
       </c>
@@ -3512,12 +3546,12 @@
         <v>35</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" s="28">
         <v>2301301011</v>
       </c>
-      <c r="D38" s="47"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="28">
         <v>7</v>
       </c>
@@ -3549,7 +3583,7 @@
       <c r="C40" s="27">
         <v>2301301018</v>
       </c>
-      <c r="D40" s="45"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="27">
         <v>7</v>
       </c>
@@ -3565,7 +3599,7 @@
       <c r="C41" s="27">
         <v>2301301021</v>
       </c>
-      <c r="D41" s="46"/>
+      <c r="D41" s="50"/>
       <c r="E41" s="27">
         <v>7</v>
       </c>
@@ -3576,12 +3610,12 @@
         <v>39</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" s="27">
         <v>2301301005</v>
       </c>
-      <c r="D42" s="47"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="27">
         <v>7</v>
       </c>
@@ -3597,7 +3631,7 @@
       <c r="C43" s="10">
         <v>2301301102</v>
       </c>
-      <c r="D43" s="48"/>
+      <c r="D43" s="52"/>
       <c r="E43" s="10">
         <v>9</v>
       </c>
@@ -3610,12 +3644,12 @@
         <v>41</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="10">
         <v>2301301022</v>
       </c>
-      <c r="D44" s="46"/>
+      <c r="D44" s="50"/>
       <c r="E44" s="10">
         <v>7</v>
       </c>
@@ -3628,12 +3662,12 @@
         <v>42</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45" s="10">
         <v>2301301009</v>
       </c>
-      <c r="D45" s="47"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="10">
         <v>8</v>
       </c>
@@ -3651,7 +3685,7 @@
       <c r="C46" s="34">
         <v>2301301080</v>
       </c>
-      <c r="D46" s="49"/>
+      <c r="D46" s="79"/>
       <c r="E46" s="34"/>
       <c r="F46" s="34"/>
     </row>
@@ -3660,12 +3694,12 @@
         <v>44</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C47" s="34">
         <v>2301301090</v>
       </c>
-      <c r="D47" s="46"/>
+      <c r="D47" s="50"/>
       <c r="E47" s="34"/>
       <c r="F47" s="34"/>
     </row>
@@ -3674,12 +3708,12 @@
         <v>45</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48" s="34">
         <v>2301301015</v>
       </c>
-      <c r="D48" s="47"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="34"/>
       <c r="F48" s="34"/>
     </row>
